--- a/submission/Track_02_workbook_Nandesh_Kanagaraju.xlsx
+++ b/submission/Track_02_workbook_Nandesh_Kanagaraju.xlsx
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>tests/ (65 tests), evidence/test_output.txt, evidence/*/benchmark.json</t>
+          <t>tests/ (67 tests), evidence/test_output.txt, evidence/*/benchmark.json</t>
         </is>
       </c>
       <c r="H28" s="71" t="n"/>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="L7" s="81" t="n">
-        <v>0.8571</v>
+        <v>0.6667</v>
       </c>
       <c r="M7" s="80" t="n">
         <v>36.097</v>
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L8" s="81" t="n">
-        <v>0.7143</v>
+        <v>0.75</v>
       </c>
       <c r="M8" s="80" t="n">
         <v>28.036</v>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="L9" s="81" t="n">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="M9" s="80" t="n">
         <v>18.587</v>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="L10" s="81" t="n">
-        <v>0.4286</v>
+        <v>0.6667</v>
       </c>
       <c r="M10" s="80" t="n">
         <v>18.799</v>
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="L11" s="81" t="n">
-        <v>0.5714</v>
+        <v>0.5</v>
       </c>
       <c r="M11" s="80" t="n">
         <v>18.982</v>
@@ -3464,7 +3464,7 @@
         </is>
       </c>
       <c r="L12" s="81" t="n">
-        <v>0.2857</v>
+        <v>0.5</v>
       </c>
       <c r="M12" s="80" t="n">
         <v>18.712</v>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="L13" s="81" t="n">
-        <v>0.8571</v>
+        <v>0.6667</v>
       </c>
       <c r="M13" s="80" t="n">
         <v>4.273</v>
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="L14" s="81" t="n">
-        <v>0.7143</v>
+        <v>0.75</v>
       </c>
       <c r="M14" s="80" t="n">
         <v>2.188</v>
@@ -3687,7 +3687,7 @@
         </is>
       </c>
       <c r="L15" s="81" t="n">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="M15" s="80" t="n">
         <v>2.187</v>
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="L16" s="81" t="n">
-        <v>0.4286</v>
+        <v>0.6667</v>
       </c>
       <c r="M16" s="80" t="n">
         <v>2.206</v>
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="L17" s="81" t="n">
-        <v>0.5714</v>
+        <v>0.5</v>
       </c>
       <c r="M17" s="80" t="n">
         <v>2.206</v>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="L18" s="81" t="n">
-        <v>0.2857</v>
+        <v>0.5</v>
       </c>
       <c r="M18" s="80" t="n">
         <v>2.227</v>
@@ -3979,7 +3979,7 @@
         </is>
       </c>
       <c r="L19" s="81" t="n">
-        <v>0.8571</v>
+        <v>0.8333</v>
       </c>
       <c r="M19" s="80" t="n">
         <v>25.194</v>
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="L20" s="81" t="n">
-        <v>0.5714</v>
+        <v>0.75</v>
       </c>
       <c r="M20" s="80" t="n">
         <v>0.45</v>
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="L21" s="81" t="n">
-        <v>0.75</v>
+        <v>0.9167</v>
       </c>
       <c r="M21" s="80" t="n">
         <v>0.438</v>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="L22" s="81" t="n">
-        <v>0.5714</v>
+        <v>0.8333</v>
       </c>
       <c r="M22" s="80" t="n">
         <v>0.443</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="L23" s="81" t="n">
-        <v>0.5714</v>
+        <v>0.75</v>
       </c>
       <c r="M23" s="80" t="n">
         <v>0.435</v>
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="L24" s="81" t="n">
-        <v>0.7143</v>
+        <v>0.8</v>
       </c>
       <c r="M24" s="80" t="n">
         <v>0.445</v>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="L25" s="81" t="n">
-        <v>0.5714</v>
+        <v>0.6667</v>
       </c>
       <c r="M25" s="80" t="n">
         <v>30.83</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="L26" s="81" t="n">
-        <v>0.4286</v>
+        <v>0.5</v>
       </c>
       <c r="M26" s="80" t="n">
         <v>0.747</v>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.7143</v>
+        <v>0.8333</v>
       </c>
       <c r="M27" t="n">
         <v>0.75</v>
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0.7143</v>
+        <v>0.75</v>
       </c>
       <c r="M32" t="n">
         <v>2.238</v>
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="M33" t="n">
         <v>2.251</v>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.5714</v>
+        <v>0.6667</v>
       </c>
       <c r="M34" t="n">
         <v>2.255</v>
